--- a/data/Jun/THÁNG 6.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
+++ b/data/Jun/THÁNG 6.2026- CHÂU NGÂN- ĐỐI SOÁT.xlsx
@@ -8,15 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\Jun\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD476631-0673-465E-9549-406022F8614E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C7BFF0A-FDFB-440E-AA88-BDFDFC538F22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1-6" sheetId="26" r:id="rId1"/>
+    <sheet name="2-6" sheetId="27" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1-6'!$A$2:$P$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1-6'!$A$2:$P$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2-6'!$A$2:$P$68</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="200">
   <si>
     <t>Tình trạng TT</t>
   </si>
@@ -126,13 +128,526 @@
   </si>
   <si>
     <t>T2.1.6.2026</t>
+  </si>
+  <si>
+    <t>THU 3</t>
+  </si>
+  <si>
+    <t>NGAY 2-6</t>
+  </si>
+  <si>
+    <t>T3.2.6.2026</t>
+  </si>
+  <si>
+    <t>ĐOÀN NGÂN CHÂU</t>
+  </si>
+  <si>
+    <t>Lữ Duyên</t>
+  </si>
+  <si>
+    <t>HD025178</t>
+  </si>
+  <si>
+    <t>76 Quang Trung Tăng nhơn phú B</t>
+  </si>
+  <si>
+    <t>a.quyen</t>
+  </si>
+  <si>
+    <t>c.cuong</t>
+  </si>
+  <si>
+    <t>01-06-2026</t>
+  </si>
+  <si>
+    <t>Hoàng Quỳnh</t>
+  </si>
+  <si>
+    <t>HD025159</t>
+  </si>
+  <si>
+    <t>14/9b đường 12, tăng nhơn phú B</t>
+  </si>
+  <si>
+    <t>Mi Su</t>
+  </si>
+  <si>
+    <t>HD024769</t>
+  </si>
+  <si>
+    <t>34/15/15 lien khu 2-5 kp5 binh tri dong</t>
+  </si>
+  <si>
+    <t>binh tan</t>
+  </si>
+  <si>
+    <t>AT 01-06</t>
+  </si>
+  <si>
+    <t>Hang Nguyen fb Bella Nguyễn</t>
+  </si>
+  <si>
+    <t>HD024885</t>
+  </si>
+  <si>
+    <t>10/23 chiến lược p bình trị đông</t>
+  </si>
+  <si>
+    <t>Bé Cam</t>
+  </si>
+  <si>
+    <t>HD025067</t>
+  </si>
+  <si>
+    <t>Số 7 đường 31 bình trị đông B</t>
+  </si>
+  <si>
+    <t>Bé My</t>
+  </si>
+  <si>
+    <t>HD024832</t>
+  </si>
+  <si>
+    <t>304/45 đường số 8 bình hưng hoà a</t>
+  </si>
+  <si>
+    <t>Vatana KhengEV37761</t>
+  </si>
+  <si>
+    <t>HD024765</t>
+  </si>
+  <si>
+    <t>315/18/6 Nguyễn Thị Tú, Phường Bình Hưng Hòa B</t>
+  </si>
+  <si>
+    <t>Quyn Nguyễn</t>
+  </si>
+  <si>
+    <t>HD025074</t>
+  </si>
+  <si>
+    <t>Chung cư Emerald block C khu Celadon</t>
+  </si>
+  <si>
+    <t>tan phu</t>
+  </si>
+  <si>
+    <t>Mai Diệu Trang</t>
+  </si>
+  <si>
+    <t>HD025180</t>
+  </si>
+  <si>
+    <t>60a phạm Đinh hổ p2</t>
+  </si>
+  <si>
+    <t>Phuong Tran</t>
+  </si>
+  <si>
+    <t>HD024960</t>
+  </si>
+  <si>
+    <t>40/18 đường 27 p sơn kì</t>
+  </si>
+  <si>
+    <t>Minh Thoan</t>
+  </si>
+  <si>
+    <t>HD025166</t>
+  </si>
+  <si>
+    <t>195 tân hương p phú thọ hoà</t>
+  </si>
+  <si>
+    <t>Như Như</t>
+  </si>
+  <si>
+    <t>HD024827</t>
+  </si>
+  <si>
+    <t>Chung Cư Akari, toà AK7, 77 Võ Văn Kiệt, Phường An Lạc</t>
+  </si>
+  <si>
+    <t>Minh Anh</t>
+  </si>
+  <si>
+    <t>HD025119</t>
+  </si>
+  <si>
+    <t>1A tạ quang bửu, p6 Chung cư tara B2.17.09</t>
+  </si>
+  <si>
+    <t>Huỳnh Lê (Malaysia)</t>
+  </si>
+  <si>
+    <t>HD025207</t>
+  </si>
+  <si>
+    <t>24/5F, Ấp Đông Lân, Xã Bà Điểm</t>
+  </si>
+  <si>
+    <t>hoc mon</t>
+  </si>
+  <si>
+    <t>Huỳnh Quế Trinh</t>
+  </si>
+  <si>
+    <t>HD025151</t>
+  </si>
+  <si>
+    <t>166 đường số 1, khu phố 25, phường Bình Hưng Hòa</t>
+  </si>
+  <si>
+    <t>Minh Thuỳ</t>
+  </si>
+  <si>
+    <t>HD024970</t>
+  </si>
+  <si>
+    <t>54/208/14A Phạm Hùng, xã Bình Hưng</t>
+  </si>
+  <si>
+    <t>binh chanh</t>
+  </si>
+  <si>
+    <t>quỳnh vũ (minh hải)</t>
+  </si>
+  <si>
+    <t>HD024806</t>
+  </si>
+  <si>
+    <t>Số 17 đường số 13 phường bình hưng hòa</t>
+  </si>
+  <si>
+    <t>Linh - fb Trâm Phí</t>
+  </si>
+  <si>
+    <t>HD025073</t>
+  </si>
+  <si>
+    <t>4D4 Thảo Nguyên Sài Gòn, đường số 2, P. Long Bình</t>
+  </si>
+  <si>
+    <t>Thỏ Thỏ</t>
+  </si>
+  <si>
+    <t>HD024768</t>
+  </si>
+  <si>
+    <t>Số 1 đường số 4 kdc vĩnh quang p16</t>
+  </si>
+  <si>
+    <t>Võ Thu Hà</t>
+  </si>
+  <si>
+    <t>HD024962</t>
+  </si>
+  <si>
+    <t>262/15 lũy bán bích, hòa thạch</t>
+  </si>
+  <si>
+    <t>Huỳnh Thanh Trúc</t>
+  </si>
+  <si>
+    <t>HD024857</t>
+  </si>
+  <si>
+    <t>18 nguyễn ngọc nhựt p.tân quý</t>
+  </si>
+  <si>
+    <t>Lam Nguyễn</t>
+  </si>
+  <si>
+    <t>HD025235</t>
+  </si>
+  <si>
+    <t>18 Nguyễn thiệu lâu, hiệp Tân</t>
+  </si>
+  <si>
+    <t>hàng sỉ</t>
+  </si>
+  <si>
+    <t>Nguyễn Minh Hải</t>
+  </si>
+  <si>
+    <t>17 Đường Số 13 Bình Hưng Hoà</t>
+  </si>
+  <si>
+    <t>Ruby vo</t>
+  </si>
+  <si>
+    <t>510 kinh dương vương, phường An Lạc</t>
+  </si>
+  <si>
+    <t>BELLA TRẦN</t>
+  </si>
+  <si>
+    <t>66 đường 17 p10</t>
+  </si>
+  <si>
+    <t>người nhận: Triệu Vy _ Ciny</t>
+  </si>
+  <si>
+    <t>HD025182</t>
+  </si>
+  <si>
+    <t>HCM: 403 Tân Sơn, p12</t>
+  </si>
+  <si>
+    <t>go vap</t>
+  </si>
+  <si>
+    <t>Hoa Ban Mai</t>
+  </si>
+  <si>
+    <t>HD025160</t>
+  </si>
+  <si>
+    <t>Số 12 đường 51 P Bình Trưng Đông cũ</t>
+  </si>
+  <si>
+    <t>Chị Mỹ</t>
+  </si>
+  <si>
+    <t>HD025217</t>
+  </si>
+  <si>
+    <t>Toà Landmark 6 - Vinhomes Central Park, 720A Điện Biên Phủ, Phường Thạnh Mỹ Tây</t>
+  </si>
+  <si>
+    <t>binh thanh</t>
+  </si>
+  <si>
+    <t>W3309 - IG Mint</t>
+  </si>
+  <si>
+    <t>HD024761</t>
+  </si>
+  <si>
+    <t>375 tân thới hiệp 21, Tổ 3, Kp3</t>
+  </si>
+  <si>
+    <t>Anh Hiệp nhận cho Anh Nguyễn</t>
+  </si>
+  <si>
+    <t>HD024906</t>
+  </si>
+  <si>
+    <t>189/46A Bạch Đằng, P3</t>
+  </si>
+  <si>
+    <t>Thuỳ Dương</t>
+  </si>
+  <si>
+    <t>HD025186</t>
+  </si>
+  <si>
+    <t>1275/1 phan văn trị</t>
+  </si>
+  <si>
+    <t>kh ck shop 915k</t>
+  </si>
+  <si>
+    <t>Ngọc Giàu</t>
+  </si>
+  <si>
+    <t>HD025210</t>
+  </si>
+  <si>
+    <t>83/3g đường tam bình phường tam bình</t>
+  </si>
+  <si>
+    <t>thu duc</t>
+  </si>
+  <si>
+    <t>Khả Hân</t>
+  </si>
+  <si>
+    <t>HD025045</t>
+  </si>
+  <si>
+    <t>10 Tạ Hiện Cát Lái</t>
+  </si>
+  <si>
+    <t>Ngô Hoàng Ánh</t>
+  </si>
+  <si>
+    <t>HD025051</t>
+  </si>
+  <si>
+    <t>235 QL13 Cũ, HBP</t>
+  </si>
+  <si>
+    <t>Ái Linh</t>
+  </si>
+  <si>
+    <t>HD025029</t>
+  </si>
+  <si>
+    <t>17/2 đường số 10 p bình trưng tây</t>
+  </si>
+  <si>
+    <t>đổi hàng</t>
+  </si>
+  <si>
+    <t>Vân Bee</t>
+  </si>
+  <si>
+    <t>HD024905</t>
+  </si>
+  <si>
+    <t>302/16 lê đức thọ p6</t>
+  </si>
+  <si>
+    <t>Binh Huong</t>
+  </si>
+  <si>
+    <t>HD024786</t>
+  </si>
+  <si>
+    <t>13 đường 44 phường 14</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Minh Phượng</t>
+  </si>
+  <si>
+    <t>HD025171</t>
+  </si>
+  <si>
+    <t>ACB Lê văn Khương 225-261a Lê văn Khương, phường Hiệp Thành</t>
+  </si>
+  <si>
+    <t>TRANG TRẦN 2</t>
+  </si>
+  <si>
+    <t>1122/23/7 quang trung phường 8</t>
+  </si>
+  <si>
+    <t>Ly Clara Selena</t>
+  </si>
+  <si>
+    <t>403 tân sơn p12</t>
+  </si>
+  <si>
+    <t>jenny bouti</t>
+  </si>
+  <si>
+    <t>401 Quang trung f10</t>
+  </si>
+  <si>
+    <t>QN NGUYEN</t>
+  </si>
+  <si>
+    <t>189/46a Bạch Đằng, phường Hạnh Thông</t>
+  </si>
+  <si>
+    <t>Hoa Nhỏ</t>
+  </si>
+  <si>
+    <t>HD025169</t>
+  </si>
+  <si>
+    <t>chung cư an gia riverside lê thị chợ, p. phú thuận</t>
+  </si>
+  <si>
+    <t>c.hieu</t>
+  </si>
+  <si>
+    <t>Trang Lê</t>
+  </si>
+  <si>
+    <t>HD025174</t>
+  </si>
+  <si>
+    <t>8A Sông Thương P2</t>
+  </si>
+  <si>
+    <t>tan binh</t>
+  </si>
+  <si>
+    <t>Nguyễn Hoàng Bảo An</t>
+  </si>
+  <si>
+    <t>HD025177</t>
+  </si>
+  <si>
+    <t>Chung cư milendium 132 bến vân đồn</t>
+  </si>
+  <si>
+    <t>Mai Chi Thi Nguyen</t>
+  </si>
+  <si>
+    <t>HD024887</t>
+  </si>
+  <si>
+    <t>100/38 Dương Bá Trạc phường 2</t>
+  </si>
+  <si>
+    <t>Ánh Hồng</t>
+  </si>
+  <si>
+    <t>HD025232</t>
+  </si>
+  <si>
+    <t>266/82/50 tô hiến thành</t>
+  </si>
+  <si>
+    <t>shop chịu ship</t>
+  </si>
+  <si>
+    <t>Nguyet</t>
+  </si>
+  <si>
+    <t>HD025094</t>
+  </si>
+  <si>
+    <t>Toà nhà lux 6...Vinhomes Golden River ( Bason), 2 Nguyễn Hữu Cảnh, P. Bến Nghé</t>
+  </si>
+  <si>
+    <t>Diida pnhom Penh</t>
+  </si>
+  <si>
+    <t>HD025040</t>
+  </si>
+  <si>
+    <t>nhà xe khải nam</t>
+  </si>
+  <si>
+    <t>Trịnh Mộng Tuyền</t>
+  </si>
+  <si>
+    <t>HD025163</t>
+  </si>
+  <si>
+    <t>422 đào trí, phú thuận lock b</t>
+  </si>
+  <si>
+    <t>Kelly Phan</t>
+  </si>
+  <si>
+    <t>HD024762</t>
+  </si>
+  <si>
+    <t>240/6A lê thánh tôn bến thành</t>
+  </si>
+  <si>
+    <t>Trân Trân</t>
+  </si>
+  <si>
+    <t>HD025126</t>
+  </si>
+  <si>
+    <t>con 56 ben van don</t>
+  </si>
+  <si>
+    <t>đơn ck</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -201,8 +716,15 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -251,6 +773,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -280,7 +808,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -326,6 +854,13 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -607,6 +1142,2643 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2F958DF-2500-4E0A-8EAB-C494DB22964E}">
+  <dimension ref="A1:R71"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="9.140625" style="1"/>
+    <col min="3" max="3" width="27.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="67" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="9.140625" style="1"/>
+    <col min="12" max="12" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.42578125" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q2" s="3"/>
+    </row>
+    <row r="3" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="19"/>
+      <c r="B3" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3" s="20">
+        <v>9</v>
+      </c>
+      <c r="G3" s="20">
+        <v>900</v>
+      </c>
+      <c r="H3" s="20">
+        <v>30</v>
+      </c>
+      <c r="I3" s="20">
+        <f t="shared" ref="I3:I54" si="0">G3-H3</f>
+        <v>870</v>
+      </c>
+      <c r="J3" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="K3" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L3" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="M3" s="19"/>
+      <c r="N3" s="19"/>
+      <c r="O3" s="19"/>
+      <c r="P3" s="19"/>
+      <c r="Q3" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="19"/>
+      <c r="B4" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="F4" s="20">
+        <v>9</v>
+      </c>
+      <c r="G4" s="20">
+        <v>1460</v>
+      </c>
+      <c r="H4" s="20">
+        <v>30</v>
+      </c>
+      <c r="I4" s="20">
+        <f t="shared" si="0"/>
+        <v>1430</v>
+      </c>
+      <c r="J4" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="K4" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L4" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="M4" s="19"/>
+      <c r="N4" s="19"/>
+      <c r="O4" s="19"/>
+      <c r="P4" s="19"/>
+      <c r="Q4" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="19"/>
+      <c r="B5" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="G5" s="20">
+        <v>920</v>
+      </c>
+      <c r="H5" s="20">
+        <v>30</v>
+      </c>
+      <c r="I5" s="20">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J5" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="K5" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L5" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="M5" s="19"/>
+      <c r="N5" s="19"/>
+      <c r="O5" s="19"/>
+      <c r="P5" s="19"/>
+      <c r="Q5" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="19"/>
+      <c r="B6" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="G6" s="20">
+        <v>870</v>
+      </c>
+      <c r="H6" s="20">
+        <v>30</v>
+      </c>
+      <c r="I6" s="20">
+        <f t="shared" si="0"/>
+        <v>840</v>
+      </c>
+      <c r="J6" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="K6" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L6" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="M6" s="19"/>
+      <c r="N6" s="19"/>
+      <c r="O6" s="19"/>
+      <c r="P6" s="19"/>
+      <c r="Q6" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="19"/>
+      <c r="B7" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="G7" s="20">
+        <v>920</v>
+      </c>
+      <c r="H7" s="20">
+        <v>30</v>
+      </c>
+      <c r="I7" s="20">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J7" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="K7" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L7" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="M7" s="19"/>
+      <c r="N7" s="19"/>
+      <c r="O7" s="19"/>
+      <c r="P7" s="19"/>
+      <c r="Q7" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="19"/>
+      <c r="B8" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="G8" s="20">
+        <v>910</v>
+      </c>
+      <c r="H8" s="20">
+        <v>30</v>
+      </c>
+      <c r="I8" s="20">
+        <f t="shared" si="0"/>
+        <v>880</v>
+      </c>
+      <c r="J8" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="K8" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L8" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="M8" s="19"/>
+      <c r="N8" s="19"/>
+      <c r="O8" s="19"/>
+      <c r="P8" s="19"/>
+      <c r="Q8" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="19"/>
+      <c r="B9" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="G9" s="20">
+        <v>0</v>
+      </c>
+      <c r="H9" s="20">
+        <v>30</v>
+      </c>
+      <c r="I9" s="20">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J9" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="K9" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L9" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="M9" s="19"/>
+      <c r="N9" s="19"/>
+      <c r="O9" s="19"/>
+      <c r="P9" s="19"/>
+      <c r="Q9" s="19">
+        <v>1</v>
+      </c>
+      <c r="R9" s="21">
+        <f>H9</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="19"/>
+      <c r="B10" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="G10" s="20">
+        <v>915</v>
+      </c>
+      <c r="H10" s="20">
+        <v>25</v>
+      </c>
+      <c r="I10" s="20">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J10" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="K10" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L10" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="M10" s="19"/>
+      <c r="N10" s="19"/>
+      <c r="O10" s="19"/>
+      <c r="P10" s="19"/>
+      <c r="Q10" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="19"/>
+      <c r="B11" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="F11" s="20">
+        <v>6</v>
+      </c>
+      <c r="G11" s="20">
+        <v>915</v>
+      </c>
+      <c r="H11" s="20">
+        <v>25</v>
+      </c>
+      <c r="I11" s="20">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J11" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="K11" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L11" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="M11" s="19"/>
+      <c r="N11" s="19"/>
+      <c r="O11" s="19"/>
+      <c r="P11" s="19"/>
+      <c r="Q11" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="19"/>
+      <c r="B12" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="G12" s="20">
+        <v>385</v>
+      </c>
+      <c r="H12" s="20">
+        <v>25</v>
+      </c>
+      <c r="I12" s="20">
+        <f t="shared" si="0"/>
+        <v>360</v>
+      </c>
+      <c r="J12" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="K12" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L12" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="M12" s="19"/>
+      <c r="N12" s="19"/>
+      <c r="O12" s="19"/>
+      <c r="P12" s="19"/>
+      <c r="Q12" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="19"/>
+      <c r="B13" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="F13" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="G13" s="20">
+        <v>0</v>
+      </c>
+      <c r="H13" s="20">
+        <v>25</v>
+      </c>
+      <c r="I13" s="20">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J13" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="K13" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L13" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="M13" s="19"/>
+      <c r="N13" s="19"/>
+      <c r="O13" s="19"/>
+      <c r="P13" s="19"/>
+      <c r="Q13" s="19">
+        <v>1</v>
+      </c>
+      <c r="R13" s="21">
+        <f>H13</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="19"/>
+      <c r="B14" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="F14" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="G14" s="20">
+        <v>920</v>
+      </c>
+      <c r="H14" s="20">
+        <v>30</v>
+      </c>
+      <c r="I14" s="20">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J14" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="K14" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L14" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="M14" s="19"/>
+      <c r="N14" s="19"/>
+      <c r="O14" s="19"/>
+      <c r="P14" s="19"/>
+      <c r="Q14" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="19"/>
+      <c r="B15" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="F15" s="20">
+        <v>8</v>
+      </c>
+      <c r="G15" s="20">
+        <v>1810</v>
+      </c>
+      <c r="H15" s="20">
+        <v>30</v>
+      </c>
+      <c r="I15" s="20">
+        <f t="shared" si="0"/>
+        <v>1780</v>
+      </c>
+      <c r="J15" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="K15" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L15" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="M15" s="19"/>
+      <c r="N15" s="19"/>
+      <c r="O15" s="19"/>
+      <c r="P15" s="19"/>
+      <c r="Q15" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="19"/>
+      <c r="B16" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="E16" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="F16" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="G16" s="20">
+        <v>0</v>
+      </c>
+      <c r="H16" s="20">
+        <v>35</v>
+      </c>
+      <c r="I16" s="20">
+        <f t="shared" si="0"/>
+        <v>-35</v>
+      </c>
+      <c r="J16" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="K16" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L16" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="M16" s="19"/>
+      <c r="N16" s="19"/>
+      <c r="O16" s="19"/>
+      <c r="P16" s="19"/>
+      <c r="Q16" s="19">
+        <v>1</v>
+      </c>
+      <c r="R16" s="21">
+        <f>H16</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="19"/>
+      <c r="B17" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="D17" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="E17" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="F17" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="G17" s="20">
+        <v>940</v>
+      </c>
+      <c r="H17" s="20">
+        <v>30</v>
+      </c>
+      <c r="I17" s="20">
+        <f t="shared" si="0"/>
+        <v>910</v>
+      </c>
+      <c r="J17" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="K17" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L17" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="M17" s="19"/>
+      <c r="N17" s="19"/>
+      <c r="O17" s="19"/>
+      <c r="P17" s="19"/>
+      <c r="Q17" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="19"/>
+      <c r="B18" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="D18" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="E18" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="F18" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="G18" s="20">
+        <v>1025</v>
+      </c>
+      <c r="H18" s="20">
+        <v>35</v>
+      </c>
+      <c r="I18" s="20">
+        <f t="shared" si="0"/>
+        <v>990</v>
+      </c>
+      <c r="J18" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="K18" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L18" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="M18" s="19"/>
+      <c r="N18" s="19"/>
+      <c r="O18" s="19"/>
+      <c r="P18" s="19"/>
+      <c r="Q18" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="19"/>
+      <c r="B19" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="D19" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="F19" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="G19" s="20">
+        <v>0</v>
+      </c>
+      <c r="H19" s="20">
+        <v>30</v>
+      </c>
+      <c r="I19" s="20">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J19" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="K19" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L19" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="M19" s="19"/>
+      <c r="N19" s="19"/>
+      <c r="O19" s="19"/>
+      <c r="P19" s="19"/>
+      <c r="Q19" s="19">
+        <v>1</v>
+      </c>
+      <c r="R19" s="21">
+        <f>H19</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="19"/>
+      <c r="B20" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="F20" s="20">
+        <v>9</v>
+      </c>
+      <c r="G20" s="20">
+        <v>690</v>
+      </c>
+      <c r="H20" s="20">
+        <v>30</v>
+      </c>
+      <c r="I20" s="20">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="J20" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="K20" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L20" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="M20" s="19"/>
+      <c r="N20" s="19"/>
+      <c r="O20" s="19"/>
+      <c r="P20" s="19"/>
+      <c r="Q20" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="19"/>
+      <c r="B21" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="D21" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="E21" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="F21" s="20">
+        <v>8</v>
+      </c>
+      <c r="G21" s="20">
+        <v>670</v>
+      </c>
+      <c r="H21" s="20">
+        <v>30</v>
+      </c>
+      <c r="I21" s="20">
+        <f t="shared" si="0"/>
+        <v>640</v>
+      </c>
+      <c r="J21" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="K21" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L21" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="M21" s="19"/>
+      <c r="N21" s="19"/>
+      <c r="O21" s="19"/>
+      <c r="P21" s="19"/>
+      <c r="Q21" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="19"/>
+      <c r="B22" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="D22" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="E22" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="F22" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="G22" s="20">
+        <v>0</v>
+      </c>
+      <c r="H22" s="20">
+        <v>25</v>
+      </c>
+      <c r="I22" s="20">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J22" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="K22" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L22" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="M22" s="19"/>
+      <c r="N22" s="19"/>
+      <c r="O22" s="19"/>
+      <c r="P22" s="19"/>
+      <c r="Q22" s="19">
+        <v>1</v>
+      </c>
+      <c r="R22" s="21">
+        <f>H22</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="19"/>
+      <c r="B23" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="D23" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="E23" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="F23" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="G23" s="20">
+        <v>685</v>
+      </c>
+      <c r="H23" s="20">
+        <v>25</v>
+      </c>
+      <c r="I23" s="20">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="J23" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="K23" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L23" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="M23" s="19"/>
+      <c r="N23" s="19"/>
+      <c r="O23" s="19"/>
+      <c r="P23" s="19"/>
+      <c r="Q23" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="19"/>
+      <c r="B24" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="D24" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="E24" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="F24" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="G24" s="20">
+        <v>895</v>
+      </c>
+      <c r="H24" s="20">
+        <v>25</v>
+      </c>
+      <c r="I24" s="20">
+        <f t="shared" si="0"/>
+        <v>870</v>
+      </c>
+      <c r="J24" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="K24" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L24" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="M24" s="19"/>
+      <c r="N24" s="19"/>
+      <c r="O24" s="19"/>
+      <c r="P24" s="19"/>
+      <c r="Q24" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="B25" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="F25" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="G25" s="20">
+        <v>0</v>
+      </c>
+      <c r="H25" s="20">
+        <v>35</v>
+      </c>
+      <c r="I25" s="20">
+        <f t="shared" si="0"/>
+        <v>-35</v>
+      </c>
+      <c r="J25" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="K25" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L25" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="M25" s="19"/>
+      <c r="N25" s="19"/>
+      <c r="O25" s="19"/>
+      <c r="P25" s="19"/>
+      <c r="Q25" s="19">
+        <v>1</v>
+      </c>
+      <c r="R25" s="21">
+        <f>H25</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="B26" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="F26" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="G26" s="20">
+        <v>35</v>
+      </c>
+      <c r="H26" s="20">
+        <v>35</v>
+      </c>
+      <c r="I26" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J26" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="K26" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L26" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="M26" s="19"/>
+      <c r="N26" s="19"/>
+      <c r="O26" s="19"/>
+      <c r="P26" s="19"/>
+      <c r="Q26" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="B27" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C27" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="F27" s="20">
+        <v>6</v>
+      </c>
+      <c r="G27" s="20">
+        <v>0</v>
+      </c>
+      <c r="H27" s="20">
+        <v>30</v>
+      </c>
+      <c r="I27" s="20">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J27" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="K27" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L27" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="M27" s="19"/>
+      <c r="N27" s="19"/>
+      <c r="O27" s="19"/>
+      <c r="P27" s="19"/>
+      <c r="Q27" s="19">
+        <v>1</v>
+      </c>
+      <c r="R27" s="21">
+        <f>H27</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="19"/>
+      <c r="B28" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="D28" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="E28" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="F28" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="G28" s="20">
+        <v>15</v>
+      </c>
+      <c r="H28" s="20">
+        <v>15</v>
+      </c>
+      <c r="I28" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J28" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="K28" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L28" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="M28" s="19"/>
+      <c r="N28" s="19"/>
+      <c r="O28" s="19"/>
+      <c r="P28" s="19"/>
+      <c r="Q28" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="19"/>
+      <c r="B29" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C29" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="D29" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="E29" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="F29" s="20">
+        <v>2</v>
+      </c>
+      <c r="G29" s="20">
+        <v>720</v>
+      </c>
+      <c r="H29" s="20">
+        <v>30</v>
+      </c>
+      <c r="I29" s="20">
+        <f t="shared" si="0"/>
+        <v>690</v>
+      </c>
+      <c r="J29" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="K29" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L29" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="M29" s="19"/>
+      <c r="N29" s="19"/>
+      <c r="O29" s="19"/>
+      <c r="P29" s="19"/>
+      <c r="Q29" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="19"/>
+      <c r="B30" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C30" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="D30" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="E30" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="F30" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="G30" s="20">
+        <v>370</v>
+      </c>
+      <c r="H30" s="20">
+        <v>20</v>
+      </c>
+      <c r="I30" s="20">
+        <f t="shared" si="0"/>
+        <v>350</v>
+      </c>
+      <c r="J30" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="K30" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L30" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="M30" s="19"/>
+      <c r="N30" s="19"/>
+      <c r="O30" s="19"/>
+      <c r="P30" s="19"/>
+      <c r="Q30" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="19"/>
+      <c r="B31" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C31" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="D31" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="E31" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="F31" s="20">
+        <v>12</v>
+      </c>
+      <c r="G31" s="20">
+        <v>0</v>
+      </c>
+      <c r="H31" s="20">
+        <v>40</v>
+      </c>
+      <c r="I31" s="20">
+        <f t="shared" si="0"/>
+        <v>-40</v>
+      </c>
+      <c r="J31" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="K31" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L31" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="M31" s="19"/>
+      <c r="N31" s="19"/>
+      <c r="O31" s="19"/>
+      <c r="P31" s="19"/>
+      <c r="Q31" s="19">
+        <v>1</v>
+      </c>
+      <c r="R31" s="21">
+        <f>H31</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="19"/>
+      <c r="B32" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C32" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="D32" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="E32" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="F32" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="G32" s="20">
+        <v>535</v>
+      </c>
+      <c r="H32" s="20">
+        <v>25</v>
+      </c>
+      <c r="I32" s="20">
+        <f t="shared" si="0"/>
+        <v>510</v>
+      </c>
+      <c r="J32" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="K32" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L32" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="M32" s="19"/>
+      <c r="N32" s="19"/>
+      <c r="O32" s="19"/>
+      <c r="P32" s="19"/>
+      <c r="Q32" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="19"/>
+      <c r="B33" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C33" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="D33" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="E33" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="F33" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="G33" s="20">
+        <v>0</v>
+      </c>
+      <c r="H33" s="20">
+        <v>25</v>
+      </c>
+      <c r="I33" s="20">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J33" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="K33" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L33" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="M33" s="23" t="s">
+        <v>134</v>
+      </c>
+      <c r="N33" s="19"/>
+      <c r="O33" s="19"/>
+      <c r="P33" s="19"/>
+      <c r="Q33" s="19">
+        <v>1</v>
+      </c>
+      <c r="R33" s="21">
+        <f>H33</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="19"/>
+      <c r="B34" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C34" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="D34" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="E34" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="F34" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="G34" s="20">
+        <v>0</v>
+      </c>
+      <c r="H34" s="20">
+        <v>30</v>
+      </c>
+      <c r="I34" s="20">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J34" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="K34" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L34" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="M34" s="19"/>
+      <c r="N34" s="19"/>
+      <c r="O34" s="19"/>
+      <c r="P34" s="19"/>
+      <c r="Q34" s="19">
+        <v>1</v>
+      </c>
+      <c r="R34" s="21">
+        <f>H34</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="19"/>
+      <c r="B35" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C35" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="D35" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="E35" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="F35" s="20">
+        <v>2</v>
+      </c>
+      <c r="G35" s="20">
+        <v>900</v>
+      </c>
+      <c r="H35" s="20">
+        <v>30</v>
+      </c>
+      <c r="I35" s="20">
+        <f t="shared" si="0"/>
+        <v>870</v>
+      </c>
+      <c r="J35" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="K35" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L35" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="M35" s="19"/>
+      <c r="N35" s="19"/>
+      <c r="O35" s="19"/>
+      <c r="P35" s="19"/>
+      <c r="Q35" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="19"/>
+      <c r="B36" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C36" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="D36" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="E36" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="F36" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="G36" s="20">
+        <v>900</v>
+      </c>
+      <c r="H36" s="20">
+        <v>30</v>
+      </c>
+      <c r="I36" s="20">
+        <f t="shared" si="0"/>
+        <v>870</v>
+      </c>
+      <c r="J36" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="K36" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L36" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="M36" s="19"/>
+      <c r="N36" s="19"/>
+      <c r="O36" s="19"/>
+      <c r="P36" s="19"/>
+      <c r="Q36" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="24"/>
+      <c r="B37" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" s="24" t="s">
+        <v>145</v>
+      </c>
+      <c r="D37" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="E37" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="F37" s="25">
+        <v>2</v>
+      </c>
+      <c r="G37" s="25">
+        <v>0</v>
+      </c>
+      <c r="H37" s="25">
+        <v>30</v>
+      </c>
+      <c r="I37" s="25">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J37" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="K37" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="L37" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="M37" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="N37" s="24"/>
+      <c r="O37" s="24"/>
+      <c r="P37" s="24"/>
+      <c r="Q37" s="24">
+        <v>1</v>
+      </c>
+      <c r="R37" s="26">
+        <f>H37</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="19"/>
+      <c r="B38" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C38" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="D38" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="E38" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="F38" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="G38" s="20">
+        <v>515</v>
+      </c>
+      <c r="H38" s="20">
+        <v>25</v>
+      </c>
+      <c r="I38" s="20">
+        <f t="shared" si="0"/>
+        <v>490</v>
+      </c>
+      <c r="J38" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="K38" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L38" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="M38" s="19"/>
+      <c r="N38" s="19"/>
+      <c r="O38" s="19"/>
+      <c r="P38" s="19"/>
+      <c r="Q38" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="19"/>
+      <c r="B39" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C39" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="D39" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="E39" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="F39" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="G39" s="20">
+        <v>765</v>
+      </c>
+      <c r="H39" s="20">
+        <v>25</v>
+      </c>
+      <c r="I39" s="20">
+        <f t="shared" si="0"/>
+        <v>740</v>
+      </c>
+      <c r="J39" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="K39" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L39" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="M39" s="19"/>
+      <c r="N39" s="19"/>
+      <c r="O39" s="19"/>
+      <c r="P39" s="19"/>
+      <c r="Q39" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="19"/>
+      <c r="B40" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C40" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="D40" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="E40" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="F40" s="20">
+        <v>12</v>
+      </c>
+      <c r="G40" s="20">
+        <v>920</v>
+      </c>
+      <c r="H40" s="20">
+        <v>30</v>
+      </c>
+      <c r="I40" s="20">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J40" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="K40" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L40" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="M40" s="19"/>
+      <c r="N40" s="19"/>
+      <c r="O40" s="19"/>
+      <c r="P40" s="19"/>
+      <c r="Q40" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="B41" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C41" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="D41" s="19"/>
+      <c r="E41" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="F41" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="G41" s="20">
+        <v>35</v>
+      </c>
+      <c r="H41" s="20">
+        <v>35</v>
+      </c>
+      <c r="I41" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J41" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="K41" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L41" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="M41" s="19"/>
+      <c r="N41" s="19"/>
+      <c r="O41" s="19"/>
+      <c r="P41" s="19"/>
+      <c r="Q41" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="B42" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C42" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="D42" s="19"/>
+      <c r="E42" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="F42" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="G42" s="20">
+        <v>0</v>
+      </c>
+      <c r="H42" s="20">
+        <v>30</v>
+      </c>
+      <c r="I42" s="20">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J42" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="K42" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L42" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="M42" s="19"/>
+      <c r="N42" s="19"/>
+      <c r="O42" s="19"/>
+      <c r="P42" s="19"/>
+      <c r="Q42" s="19">
+        <v>1</v>
+      </c>
+      <c r="R42" s="21">
+        <f>H42</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="B43" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C43" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="D43" s="19"/>
+      <c r="E43" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="F43" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="G43" s="20">
+        <v>4540</v>
+      </c>
+      <c r="H43" s="20">
+        <v>40</v>
+      </c>
+      <c r="I43" s="20">
+        <f t="shared" si="0"/>
+        <v>4500</v>
+      </c>
+      <c r="J43" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="K43" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L43" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="M43" s="19"/>
+      <c r="N43" s="19"/>
+      <c r="O43" s="19"/>
+      <c r="P43" s="19"/>
+      <c r="Q43" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="B44" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C44" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="D44" s="19"/>
+      <c r="E44" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="F44" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="G44" s="20">
+        <v>0</v>
+      </c>
+      <c r="H44" s="20">
+        <v>30</v>
+      </c>
+      <c r="I44" s="20">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J44" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="K44" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L44" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="M44" s="19"/>
+      <c r="N44" s="19"/>
+      <c r="O44" s="19"/>
+      <c r="P44" s="19"/>
+      <c r="Q44" s="19">
+        <v>1</v>
+      </c>
+      <c r="R44" s="21">
+        <f>H44</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="19"/>
+      <c r="B45" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C45" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="D45" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="E45" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="F45" s="20">
+        <v>7</v>
+      </c>
+      <c r="G45" s="20">
+        <v>550</v>
+      </c>
+      <c r="H45" s="20">
+        <v>30</v>
+      </c>
+      <c r="I45" s="20">
+        <f t="shared" si="0"/>
+        <v>520</v>
+      </c>
+      <c r="J45" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="K45" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L45" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="M45" s="19"/>
+      <c r="N45" s="19"/>
+      <c r="O45" s="19"/>
+      <c r="P45" s="19"/>
+      <c r="Q45" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="19"/>
+      <c r="B46" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C46" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="D46" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="E46" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="F46" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="G46" s="20">
+        <v>1015</v>
+      </c>
+      <c r="H46" s="20">
+        <v>25</v>
+      </c>
+      <c r="I46" s="20">
+        <f t="shared" si="0"/>
+        <v>990</v>
+      </c>
+      <c r="J46" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="K46" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L46" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="M46" s="19"/>
+      <c r="N46" s="19"/>
+      <c r="O46" s="19"/>
+      <c r="P46" s="19"/>
+      <c r="Q46" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="19"/>
+      <c r="B47" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C47" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="D47" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="E47" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="F47" s="20">
+        <v>4</v>
+      </c>
+      <c r="G47" s="20">
+        <v>895</v>
+      </c>
+      <c r="H47" s="20">
+        <v>25</v>
+      </c>
+      <c r="I47" s="20">
+        <f t="shared" si="0"/>
+        <v>870</v>
+      </c>
+      <c r="J47" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="K47" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L47" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="M47" s="19"/>
+      <c r="N47" s="19"/>
+      <c r="O47" s="19"/>
+      <c r="P47" s="19"/>
+      <c r="Q47" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="19"/>
+      <c r="B48" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C48" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="D48" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="E48" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="F48" s="20">
+        <v>8</v>
+      </c>
+      <c r="G48" s="20">
+        <v>620</v>
+      </c>
+      <c r="H48" s="20">
+        <v>30</v>
+      </c>
+      <c r="I48" s="20">
+        <f t="shared" si="0"/>
+        <v>590</v>
+      </c>
+      <c r="J48" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="K48" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L48" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="M48" s="19"/>
+      <c r="N48" s="19"/>
+      <c r="O48" s="19"/>
+      <c r="P48" s="19"/>
+      <c r="Q48" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="19"/>
+      <c r="B49" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C49" s="19" t="s">
+        <v>180</v>
+      </c>
+      <c r="D49" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="E49" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="F49" s="20">
+        <v>10</v>
+      </c>
+      <c r="G49" s="20">
+        <v>3260</v>
+      </c>
+      <c r="H49" s="20">
+        <v>35</v>
+      </c>
+      <c r="I49" s="20">
+        <f t="shared" si="0"/>
+        <v>3225</v>
+      </c>
+      <c r="J49" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="K49" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L49" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="M49" s="23" t="s">
+        <v>183</v>
+      </c>
+      <c r="N49" s="19"/>
+      <c r="O49" s="19"/>
+      <c r="P49" s="19"/>
+      <c r="Q49" s="19">
+        <v>1</v>
+      </c>
+      <c r="R49" s="21">
+        <f>H49</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="19"/>
+      <c r="B50" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C50" s="19" t="s">
+        <v>184</v>
+      </c>
+      <c r="D50" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="E50" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="F50" s="20">
+        <v>1</v>
+      </c>
+      <c r="G50" s="20">
+        <v>915</v>
+      </c>
+      <c r="H50" s="20">
+        <v>25</v>
+      </c>
+      <c r="I50" s="20">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J50" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="K50" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L50" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="M50" s="19"/>
+      <c r="N50" s="19"/>
+      <c r="O50" s="19"/>
+      <c r="P50" s="19"/>
+      <c r="Q50" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="19"/>
+      <c r="B51" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C51" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="D51" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="E51" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="F51" s="20">
+        <v>5</v>
+      </c>
+      <c r="G51" s="20">
+        <v>0</v>
+      </c>
+      <c r="H51" s="20">
+        <v>25</v>
+      </c>
+      <c r="I51" s="20">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J51" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="K51" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L51" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="M51" s="19"/>
+      <c r="N51" s="19"/>
+      <c r="O51" s="19"/>
+      <c r="P51" s="19"/>
+      <c r="Q51" s="19">
+        <v>1</v>
+      </c>
+      <c r="R51" s="21">
+        <f>H51</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="19"/>
+      <c r="B52" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C52" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="D52" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="E52" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="F52" s="20">
+        <v>7</v>
+      </c>
+      <c r="G52" s="20">
+        <v>2690</v>
+      </c>
+      <c r="H52" s="20">
+        <v>35</v>
+      </c>
+      <c r="I52" s="20">
+        <f t="shared" si="0"/>
+        <v>2655</v>
+      </c>
+      <c r="J52" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="K52" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L52" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="M52" s="23" t="s">
+        <v>183</v>
+      </c>
+      <c r="N52" s="19"/>
+      <c r="O52" s="19"/>
+      <c r="P52" s="19"/>
+      <c r="Q52" s="19">
+        <v>1</v>
+      </c>
+      <c r="R52" s="21">
+        <f>H52</f>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="24"/>
+      <c r="B53" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="C53" s="24" t="s">
+        <v>193</v>
+      </c>
+      <c r="D53" s="24" t="s">
+        <v>194</v>
+      </c>
+      <c r="E53" s="24" t="s">
+        <v>195</v>
+      </c>
+      <c r="F53" s="25">
+        <v>1</v>
+      </c>
+      <c r="G53" s="25">
+        <v>0</v>
+      </c>
+      <c r="H53" s="25">
+        <v>25</v>
+      </c>
+      <c r="I53" s="25">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J53" s="24" t="s">
+        <v>169</v>
+      </c>
+      <c r="K53" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="L53" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="M53" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="N53" s="24"/>
+      <c r="O53" s="24"/>
+      <c r="P53" s="24"/>
+      <c r="Q53" s="24">
+        <v>1</v>
+      </c>
+      <c r="R53" s="26">
+        <f>H53</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="19"/>
+      <c r="B54" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C54" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="D54" s="19" t="s">
+        <v>197</v>
+      </c>
+      <c r="E54" s="19" t="s">
+        <v>198</v>
+      </c>
+      <c r="F54" s="20">
+        <v>4</v>
+      </c>
+      <c r="G54" s="20">
+        <v>1905</v>
+      </c>
+      <c r="H54" s="20">
+        <v>25</v>
+      </c>
+      <c r="I54" s="20">
+        <f t="shared" si="0"/>
+        <v>1880</v>
+      </c>
+      <c r="J54" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="K54" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="L54" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="M54" s="19"/>
+      <c r="N54" s="19"/>
+      <c r="O54" s="19"/>
+      <c r="P54" s="19"/>
+      <c r="Q54" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="G56" s="1">
+        <f>SUBTOTAL(9,G3:G54)</f>
+        <v>37930</v>
+      </c>
+      <c r="H56" s="1">
+        <f t="shared" ref="H56:R56" si="1">SUBTOTAL(9,H3:H54)</f>
+        <v>1505</v>
+      </c>
+      <c r="I56" s="1">
+        <f t="shared" si="1"/>
+        <v>36425</v>
+      </c>
+      <c r="J56" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K56" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L56" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M56" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N56" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O56" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P56" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q56" s="1">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="R56" s="1">
+        <f t="shared" si="1"/>
+        <v>515</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H60" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I60" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J60" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H61" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I61" s="8">
+        <f>SUM(I55:I59)</f>
+        <v>36425</v>
+      </c>
+      <c r="J61" s="8">
+        <f>Q56</f>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H62" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I62" s="10">
+        <f>R56</f>
+        <v>515</v>
+      </c>
+      <c r="J62" s="11"/>
+    </row>
+    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H63" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="I63" s="10">
+        <f>S55</f>
+        <v>0</v>
+      </c>
+      <c r="J63" s="11"/>
+    </row>
+    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H64" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I64" s="10">
+        <f>T55</f>
+        <v>0</v>
+      </c>
+      <c r="J64" s="11"/>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H65" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I65" s="10">
+        <f>U55</f>
+        <v>0</v>
+      </c>
+      <c r="J65" s="11"/>
+    </row>
+    <row r="66" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H66" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="I66" s="13"/>
+      <c r="J66" s="13"/>
+    </row>
+    <row r="67" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H67" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="I67" s="13"/>
+      <c r="J67" s="13"/>
+    </row>
+    <row r="68" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H68" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="I68" s="16">
+        <f>SUM(I61:I67)</f>
+        <v>36940</v>
+      </c>
+      <c r="J68" s="16">
+        <f>SUM(J61:J65)</f>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A71" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="B71" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="C71" s="28" t="s">
+        <v>132</v>
+      </c>
+      <c r="D71" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="E71" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="F71" s="29">
+        <v>915</v>
+      </c>
+      <c r="G71" s="29">
+        <v>0</v>
+      </c>
+      <c r="H71" s="29">
+        <f t="shared" ref="H71" si="2">F71-G71</f>
+        <v>915</v>
+      </c>
+      <c r="I71" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="J71" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="K71" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="L71" s="23" t="s">
+        <v>134</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:P54" xr:uid="{00000000-0009-0000-0000-000006000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P54">
+      <sortCondition ref="J2:J54"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3A406E0-A4A6-43FE-AF8E-4E3639F28E7A}">
   <dimension ref="A1:R82"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -623,10 +3795,10 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
@@ -1951,11 +5123,11 @@
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.25">
       <c r="G70" s="1">
-        <f t="shared" ref="G70:R70" si="0">SUBTOTAL(9,G25:G69)</f>
+        <f>SUBTOTAL(9,G3:G68)</f>
         <v>0</v>
       </c>
       <c r="H70" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="H70:R70" si="0">SUBTOTAL(9,H3:H68)</f>
         <v>0</v>
       </c>
       <c r="I70" s="1">
@@ -2001,7 +5173,7 @@
     </row>
     <row r="74" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H74" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="I74" s="5" t="s">
         <v>15</v>
